--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2018_T4_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2018_T4_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>86</t>
+    <t>82</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>2.928</t>
-  </si>
-  <si>
-    <t>(0.463)</t>
-  </si>
-  <si>
-    <t>15.535</t>
-  </si>
-  <si>
-    <t>(1.979)</t>
-  </si>
-  <si>
-    <t>89.499</t>
-  </si>
-  <si>
-    <t>(24.308)</t>
-  </si>
-  <si>
-    <t>109.015</t>
-  </si>
-  <si>
-    <t>(30.132)</t>
-  </si>
-  <si>
-    <t>2.653</t>
-  </si>
-  <si>
-    <t>(0.324)</t>
-  </si>
-  <si>
-    <t>15.767</t>
-  </si>
-  <si>
-    <t>(2.008)</t>
-  </si>
-  <si>
-    <t>6.353</t>
-  </si>
-  <si>
-    <t>(1.264)</t>
-  </si>
-  <si>
-    <t>7.582</t>
-  </si>
-  <si>
-    <t>(6.450)</t>
-  </si>
-  <si>
-    <t>117.746</t>
-  </si>
-  <si>
-    <t>(30.055)</t>
-  </si>
-  <si>
-    <t>104.318</t>
-  </si>
-  <si>
-    <t>(31.240)</t>
+    <t>2.748</t>
+  </si>
+  <si>
+    <t>(0.385)</t>
+  </si>
+  <si>
+    <t>16.268</t>
+  </si>
+  <si>
+    <t>(2.041)</t>
+  </si>
+  <si>
+    <t>61.281</t>
+  </si>
+  <si>
+    <t>(11.885)</t>
+  </si>
+  <si>
+    <t>73.270</t>
+  </si>
+  <si>
+    <t>(13.043)</t>
+  </si>
+  <si>
+    <t>2.702</t>
+  </si>
+  <si>
+    <t>(0.332)</t>
+  </si>
+  <si>
+    <t>16.390</t>
+  </si>
+  <si>
+    <t>(2.078)</t>
+  </si>
+  <si>
+    <t>5.470</t>
+  </si>
+  <si>
+    <t>(1.119)</t>
+  </si>
+  <si>
+    <t>1.070</t>
+  </si>
+  <si>
+    <t>(0.194)</t>
+  </si>
+  <si>
+    <t>84.116</t>
+  </si>
+  <si>
+    <t>(14.256)</t>
+  </si>
+  <si>
+    <t>65.374</t>
+  </si>
+  <si>
+    <t>(13.016)</t>
   </si>
   <si>
     <t>28</t>
@@ -198,7 +198,7 @@
     <t>(32.419)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.240</t>
-  </si>
-  <si>
-    <t>-0.963</t>
-  </si>
-  <si>
-    <t>58.144</t>
-  </si>
-  <si>
-    <t>47.839</t>
-  </si>
-  <si>
-    <t>-0.741</t>
-  </si>
-  <si>
-    <t>-0.732</t>
-  </si>
-  <si>
-    <t>-2.821</t>
-  </si>
-  <si>
-    <t>-6.983</t>
-  </si>
-  <si>
-    <t>62.216</t>
-  </si>
-  <si>
-    <t>30.956</t>
+    <t>0.420</t>
+  </si>
+  <si>
+    <t>-1.697</t>
+  </si>
+  <si>
+    <t>86.362***</t>
+  </si>
+  <si>
+    <t>83.584***</t>
+  </si>
+  <si>
+    <t>-0.790</t>
+  </si>
+  <si>
+    <t>-1.355</t>
+  </si>
+  <si>
+    <t>-1.937</t>
+  </si>
+  <si>
+    <t>-0.470</t>
+  </si>
+  <si>
+    <t>95.847***</t>
+  </si>
+  <si>
+    <t>69.900**</t>
   </si>
 </sst>
 </file>
